--- a/astro-site/public/dl/plan-negocio-tapas-bar/checklist-apertura-tapas-bar.xlsx
+++ b/astro-site/public/dl/plan-negocio-tapas-bar/checklist-apertura-tapas-bar.xlsx
@@ -14,7 +14,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F5 - Marketing" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F6 - 90 Dias" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'F1 - Constitucion'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'F2 - Local'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'F3 - Equipamiento'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'F4 - Personal'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'F5 - Marketing'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'F6 - 90 Dias'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -22,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,6 +58,11 @@
     <font>
       <name val="Calibri"/>
       <color rgb="001A1A1A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -91,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -106,10 +118,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -469,9 +492,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -495,6 +518,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -763,13 +787,53 @@
         <is>
           <t>Proteger nombre del gastrobar</t>
         </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C15">
+        <f>COUNTIF(A5:A13,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E15">
+        <f>COUNTIF(B5:B13,"?*")</f>
+        <v>9.0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <conditionalFormatting sqref="A5:E13">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$A5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,☐,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -777,9 +841,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -803,6 +867,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1071,13 +1136,53 @@
         <is>
           <t>Obligatorio si zona residencial mixta</t>
         </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C15">
+        <f>COUNTIF(A5:A13,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E15">
+        <f>COUNTIF(B5:B13,"?*")</f>
+        <v>9.0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <conditionalFormatting sqref="A5:E13">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$A5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,☐,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1085,9 +1190,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1111,6 +1216,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1487,13 +1593,53 @@
         <is>
           <t>Azulejos, madera, pizarras tapas del dia</t>
         </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C19">
+        <f>COUNTIF(A5:A17,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E19">
+        <f>COUNTIF(B5:B17,"?*")</f>
+        <v>13.0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <conditionalFormatting sqref="A5:E17">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$A5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,☐,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1501,342 +1647,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>CHECKLIST APERTURA — TAPAS BAR / GASTROBAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>FASE 4: PERSONAL Y FORMACION</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>TRAMITE / ACCION</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>RESPONSABLE</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>PLAZO</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>NOTAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Definir organigrama y turnos</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>1 semana</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>Turno partido (almuerzo + cena) o continuo</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Publicar ofertas empleo</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>1-2 semanas</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>Buscar cocinero con experiencia en tapas</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Seleccion y entrevistas</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>2 semanas</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Prueba practica: elaborar 3 tapas en 20 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Contratos de trabajo</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Gestor</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>1 dia</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>Convenio provincial hosteleria</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Alta trabajadores Seguridad Social</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Gestor</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Antes del alta</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Minimo 1 dia antes de empezar</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Carnet manipulador alimentos</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>1 dia</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>Obligatorio todo personal, curso online valido</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Plan prevencion riesgos (PRL)</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>SPA</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>1-2 semanas</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Servicio Prevencion Ajeno obligatorio</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Formacion cocina tapas</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>Jefe cocina</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>1-2 semanas</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Estandarizar recetas, presentaciones, tiempos</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Formacion servicio y barra</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>1 semana</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Tiraje cerveza, vermut, servicio tapas en barra</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Formacion alergenos + APPCC</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>1 dia</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>14 alergenos, registro temperaturas, trazabilidad</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1858,10 +1669,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FASE 5: MARKETING Y LANZAMIENTO</t>
-        </is>
-      </c>
-    </row>
+          <t>FASE 4: PERSONAL Y FORMACION</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1897,22 +1709,22 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Disenar identidad visual</t>
+          <t>Definir organigrama y turnos</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Disenador</t>
+          <t>Titular</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>2-3 semanas</t>
+          <t>1 semana</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Logo, colores, tipografia, estilo visual</t>
+          <t>Turno partido (almuerzo + cena) o continuo</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1736,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Ficha Google My Business (CRITICO)</t>
+          <t>Publicar ofertas empleo</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -1934,12 +1746,12 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>1-2 semanas</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Categoria: Bar de tapas. Fotos, horario, carta</t>
+          <t>Buscar cocinero con experiencia en tapas</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1763,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Perfiles RRSS (Instagram + TikTok)</t>
+          <t>Seleccion y entrevistas</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -1961,12 +1773,12 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>2 semanas</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Instagram para fotos tapas, TikTok para videos cocina</t>
+          <t>Prueba practica: elaborar 3 tapas en 20 min</t>
         </is>
       </c>
     </row>
@@ -1978,22 +1790,22 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Pagina web basica</t>
+          <t>Contratos de trabajo</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Dev/Disenador</t>
+          <t>Gestor</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>1-2 semanas</t>
+          <t>1 dia</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Con carta, ubicacion, reservas, horario</t>
+          <t>Convenio provincial hosteleria</t>
         </is>
       </c>
     </row>
@@ -2005,22 +1817,22 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Sesion fotos profesional</t>
+          <t>Alta trabajadores Seguridad Social</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Fotografo</t>
+          <t>Gestor</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>Antes del alta</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Tapas, raciones, barra, ambiente, terraza</t>
+          <t>Minimo 1 dia antes de empezar</t>
         </is>
       </c>
     </row>
@@ -2032,22 +1844,22 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Disenar carta / pizarras tapas</t>
+          <t>Carnet manipulador alimentos</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Disenador</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>1 semana</t>
+          <t>1 dia</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Carta fisica + pizarra tapas del dia + QR digital</t>
+          <t>Obligatorio todo personal, curso online valido</t>
         </is>
       </c>
     </row>
@@ -2059,22 +1871,22 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Rotulacion exterior</t>
+          <t>Plan prevencion riesgos (PRL)</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Rotulista</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>1 semana</t>
+          <t>1-2 semanas</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Rotulo + pizarra exterior + vinilo</t>
+          <t>Servicio Prevencion Ajeno obligatorio</t>
         </is>
       </c>
     </row>
@@ -2086,22 +1898,22 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Campana pre-apertura RRSS</t>
+          <t>Formacion cocina tapas</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Titular</t>
+          <t>Jefe cocina</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>2-4 semanas</t>
+          <t>1-2 semanas</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Behind the scenes, cuenta atras, sorteo inaugural</t>
+          <t>Estandarizar recetas, presentaciones, tiempos</t>
         </is>
       </c>
     </row>
@@ -2113,7 +1925,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Acuerdos proveedores (cerveza, vino, vermut)</t>
+          <t>Formacion servicio y barra</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -2123,12 +1935,12 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>2 semanas</t>
+          <t>1 semana</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Negociar exclusividad cerveza por grifos gratis</t>
+          <t>Tiraje cerveza, vermut, servicio tapas en barra</t>
         </is>
       </c>
     </row>
@@ -2140,7 +1952,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Registrarse en Google Maps, TripAdvisor, TheFork</t>
+          <t>Formacion alergenos + APPCC</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -2155,79 +1967,65 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>TheFork importante para tapas con reserva</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Evento inauguracion</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>1 dia</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Invitar vecinos, influencers foodie, prensa barrio</t>
-        </is>
-      </c>
-    </row>
+          <t>14 alergenos, registro temperaturas, trazabilidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Programa fidelizacion</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>1 semana</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>Tarjeta tapas 10a gratis o app de puntos</t>
-        </is>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C16">
+        <f>COUNTIF(A5:A14,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E16">
+        <f>COUNTIF(B5:B14,"?*")</f>
+        <v>10.0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <conditionalFormatting sqref="A5:E14">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$A5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,☐,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2247,10 +2045,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FASE 6: PRIMEROS 90 DIAS</t>
-        </is>
-      </c>
-    </row>
+          <t>FASE 5: MARKETING Y LANZAMIENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2286,22 +2085,22 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Revision diaria caja y ventas</t>
+          <t>Disenar identidad visual</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Titular</t>
+          <t>Disenador</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Diario</t>
+          <t>2-3 semanas</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Comparar con previsiones plan financiero</t>
+          <t>Logo, colores, tipografia, estilo visual</t>
         </is>
       </c>
     </row>
@@ -2313,22 +2112,22 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Control food cost semanal</t>
+          <t>Ficha Google My Business (CRITICO)</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Jefe cocina</t>
+          <t>Titular</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Semanal</t>
+          <t>1 dia</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Pesar genero: carnes, pescado, embutidos</t>
+          <t>Categoria: Bar de tapas. Fotos, horario, carta</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2139,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Analisis tapas mas vendidas vs menos vendidas</t>
+          <t>Perfiles RRSS (Instagram + TikTok)</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -2350,12 +2149,12 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Mes 1</t>
+          <t>1 dia</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Aplicar ingenieria de menu: Stars, Puzzles, Dogs</t>
+          <t>Instagram para fotos tapas, TikTok para videos cocina</t>
         </is>
       </c>
     </row>
@@ -2367,22 +2166,22 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Ajustar carta tapas del dia</t>
+          <t>Pagina web basica</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Jefe cocina</t>
+          <t>Dev/Disenador</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Semanal</t>
+          <t>1-2 semanas</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Rotar tapas segun temporada y producto disponible</t>
+          <t>Con carta, ubicacion, reservas, horario</t>
         </is>
       </c>
     </row>
@@ -2394,22 +2193,22 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Encuestas clientes + resenas Google</t>
+          <t>Sesion fotos profesional</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Titular</t>
+          <t>Fotografo</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Mes 1-3</t>
+          <t>1 dia</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Pedir resenas, responder TODAS</t>
+          <t>Tapas, raciones, barra, ambiente, terraza</t>
         </is>
       </c>
     </row>
@@ -2421,22 +2220,22 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Optimizar turnos personal</t>
+          <t>Disenar carta / pizarras tapas</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Titular</t>
+          <t>Disenador</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Mes 1-2</t>
+          <t>1 semana</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Reforzar viernes-sabado, reducir lunes-martes</t>
+          <t>Carta fisica + pizarra tapas del dia + QR digital</t>
         </is>
       </c>
     </row>
@@ -2448,22 +2247,22 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Revisar proveedores y negociar</t>
+          <t>Rotulacion exterior</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Titular</t>
+          <t>Rotulista</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Mes 2</t>
+          <t>1 semana</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Con volumen real, renegociar precios cerveza, vino</t>
+          <t>Rotulo + pizarra exterior + vinilo</t>
         </is>
       </c>
     </row>
@@ -2475,7 +2274,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Evaluar delivery (Glovo, Uber Eats)</t>
+          <t>Campana pre-apertura RRSS</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -2485,12 +2284,12 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Mes 2-3</t>
+          <t>2-4 semanas</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Solo si margen lo permite (comisiones 25-35%)</t>
+          <t>Behind the scenes, cuenta atras, sorteo inaugural</t>
         </is>
       </c>
     </row>
@@ -2502,7 +2301,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Analizar competencia local</t>
+          <t>Acuerdos proveedores (cerveza, vino, vermut)</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -2512,12 +2311,12 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Mes 1</t>
+          <t>2 semanas</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Visitar otros tapas bars zona, comparar</t>
+          <t>Negociar exclusividad cerveza por grifos gratis</t>
         </is>
       </c>
     </row>
@@ -2529,29 +2328,499 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Primer cierre contable trimestral</t>
+          <t>Registrarse en Google Maps, TripAdvisor, TheFork</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Gestor</t>
+          <t>Titular</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Mes 3</t>
+          <t>1 dia</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Comparar P&amp;L real vs plan financiero</t>
-        </is>
+          <t>TheFork importante para tapas con reserva</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Evento inauguracion</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>1 dia</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Invitar vecinos, influencers foodie, prensa barrio</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Programa fidelizacion</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>1 semana</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Tarjeta tapas 10a gratis o app de puntos</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C18">
+        <f>COUNTIF(A5:A16,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E18">
+        <f>COUNTIF(B5:B16,"?*")</f>
+        <v>12.0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <conditionalFormatting sqref="A5:E16">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$A5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,☐,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CHECKLIST APERTURA — TAPAS BAR / GASTROBAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>FASE 6: PRIMEROS 90 DIAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>TRAMITE / ACCION</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>RESPONSABLE</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>PLAZO</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>NOTAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Revision diaria caja y ventas</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Diario</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Comparar con previsiones plan financiero</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Control food cost semanal</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Jefe cocina</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Semanal</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Pesar genero: carnes, pescado, embutidos</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Analisis tapas mas vendidas vs menos vendidas</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Mes 1</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Aplicar ingenieria de menu: Stars, Puzzles, Dogs</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Ajustar carta tapas del dia</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Jefe cocina</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Semanal</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Rotar tapas segun temporada y producto disponible</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Encuestas clientes + resenas Google</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Mes 1-3</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Pedir resenas, responder TODAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Optimizar turnos personal</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Mes 1-2</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Reforzar viernes-sabado, reducir lunes-martes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Revisar proveedores y negociar</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Mes 2</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Con volumen real, renegociar precios cerveza, vino</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Evaluar delivery (Glovo, Uber Eats)</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Mes 2-3</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Solo si margen lo permite (comisiones 25-35%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Analizar competencia local</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Mes 1</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Visitar otros tapas bars zona, comparar</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Primer cierre contable trimestral</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Gestor</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Mes 3</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Comparar P&amp;L real vs plan financiero</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C16">
+        <f>COUNTIF(A5:A14,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E16">
+        <f>COUNTIF(B5:B14,"?*")</f>
+        <v>10.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A5:E14">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$A5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,☐,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/plan-negocio-tapas-bar/checklist-apertura-tapas-bar.xlsx
+++ b/astro-site/public/dl/plan-negocio-tapas-bar/checklist-apertura-tapas-bar.xlsx
@@ -7,20 +7,21 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F1 - Constitucion" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F1 - Constitución" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F2 - Local" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F3 - Equipamiento" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F4 - Personal" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F5 - Marketing" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F6 - 90 Dias" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F6 - 90 Días" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'F1 - Constitucion'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'F1 - Constitución'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'F2 - Local'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'F3 - Equipamiento'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'F4 - Personal'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'F5 - Marketing'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'F6 - 90 Dias'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'F6 - 90 Días'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -29,7 +30,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,8 +66,13 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -83,6 +89,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F5F0E8"/>
         <bgColor rgb="00F5F0E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -103,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -119,16 +130,50 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00C8E6C9"/>
           <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -494,7 +539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -504,8 +549,8 @@
     <col width="40" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="90" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>CHECKLIST APERTURA — TAPAS BAR / GASTROBAR</t>
         </is>
@@ -514,7 +559,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FASE 1: CONSTITUCION Y TRAMITES LEGALES</t>
+          <t>FASE 1: CONSTITUCIÓN Y TRÁMITES LEGALES</t>
         </is>
       </c>
     </row>
@@ -527,7 +572,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>TRAMITE / ACCION</t>
+          <t>TRÁMITE / ACCIÓN</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -547,14 +592,14 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Elegir forma juridica (SL recomendada)</t>
+          <t>Elegir forma jurídica (SL recomendada)</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -569,19 +614,19 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>SL unipersonal, capital 1 EUR (Ley Crea y Crece)</t>
+          <t>SL unipersonal, capital 1 € (Ley Crea y Crece)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Constitucion SL ante notario</t>
+          <t>Constitución SL ante notario</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -591,24 +636,24 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>1-3 dias</t>
+          <t>1-3 días</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Llevar certificacion nombre, estatutos, DNI</t>
+          <t>Llevar certificación nombre, estatutos, DNI</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Inscripcion en Registro Mercantil</t>
+          <t>Inscripción en Registro Mercantil</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -618,7 +663,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>3-7 dias</t>
+          <t>3-7 días</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -628,7 +673,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -645,24 +690,24 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>1 día</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Epigrafe IAE: 673.2 (otros cafes y bares)</t>
+          <t>Epígrafe IAE: 671.5 (restaurantes de un tenedor) o 673.2 (otros cafés y bares), según el peso de la barra frente al servicio de mesa — la elección la valida tu gestor: condiciona inspecciones y licencia</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Alta Seguridad Social (autonomo + empresa)</t>
+          <t>Alta Seguridad Social (autónomo + empresa)</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -672,17 +717,17 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>1 día</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Tarifa plana autonomos 80 EUR/mes</t>
+          <t>Cuota según la base mínima del tramo que te corresponda. Consulta el importe del ejercicio en curso y verifica con tu gestoría si te aplica la cuota reducida de inicio de actividad</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -699,7 +744,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>1-3 dias</t>
+          <t>1-3 días</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -709,7 +754,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -726,24 +771,24 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>1-3 dias</t>
+          <t>1-3 días</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Imprescindible para tramites telematicos</t>
+          <t>Imprescindible para trámites telemáticos</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Registro sanitario RGSEAA</t>
+          <t>Inscripción en el Registro Sanitario de tu Comunidad Autónoma (declaración responsable de inicio de actividad alimentaria)</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -758,12 +803,12 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Obligatorio por elaboracion de alimentos</t>
+          <t>El Registro General Sanitario estatal NO aplica al minorista que sirve al consumidor final (art. 2.2 del RD 191/2011): el que te toca es el autonómico</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -789,38 +834,98 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="B15" s="8" t="inlineStr">
+    <row r="14" ht="45" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Registro de actividades de tratamiento de datos personales</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>Antes de abrir</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>Art. 30 del RGPD y art. 31 de la LOPDGDD: lo pide la AEPD en la primera inspección. Incluye clientes, personal y proveedores</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="75" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>Adaptar el TPV y la facturación al sistema Veri*factu / factura electrónica</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Gestor</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>Antes de abrir</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>El RD 1007/2023 y su calendario escalonado obligan a que el software de facturación sea verificable. Consulta la fecha que te aplica antes de comprar el TPV + comandero que presupuesta la hoja de Inversión</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C15">
-        <f>COUNTIF(A5:A13,"✓")</f>
+      <c r="C17" s="14">
+        <f>COUNTIF(A5:A15,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E15">
-        <f>COUNTIF(B5:B13,"?*")</f>
-        <v>9.0</v>
+      <c r="E17" s="14">
+        <f>COUNTIF(B5:B15,"?*")-COUNTIF(A5:A15,"N/A")</f>
+        <v>11.0</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:E13">
+  <conditionalFormatting sqref="A5:E15">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$A5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A5:A15">
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="1" stopIfTrue="1" text="✓">
+      <formula>NOT(ISERROR(SEARCH("✓",A5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
       <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -843,7 +948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -853,8 +958,8 @@
     <col width="40" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="90" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>CHECKLIST APERTURA — TAPAS BAR / GASTROBAR</t>
         </is>
@@ -876,7 +981,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>TRAMITE / ACCION</t>
+          <t>TRÁMITE / ACCIÓN</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -896,14 +1001,14 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Busqueda y seleccion de local</t>
+          <t>Búsqueda y selección de local</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -923,14 +1028,14 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Negociacion contrato alquiler</t>
+          <t>Negociación contrato alquiler</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -950,14 +1055,14 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Verificar uso urbanistico</t>
+          <t>Verificar uso urbanístico</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -972,12 +1077,12 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Informe urbanistico ANTES de firmar</t>
+          <t>Informe urbanístico ANTES de firmar</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -999,12 +1104,12 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Tapas bar con cocina = actividad clasificada (mas exigente)</t>
+          <t>Tapas bar con cocina = actividad clasificada (más exigente)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1026,19 +1131,19 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Terraza = facturacion extra 20-30%, renovacion anual</t>
+          <t>Terraza = facturación extra 20-30%, renovación anual</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Licencia de musica ambiente</t>
+          <t>Licencia de música ambiente</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -1058,7 +1163,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1075,17 +1180,17 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>1 día</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Minimo 300.000 EUR RC</t>
+          <t>Mínimo 300.000 € RC</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1102,29 +1207,29 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>1 día</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Incendio, robo, danos agua</t>
+          <t>Incendio, robo, daños agua</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Medicion acustica (si aplica)</t>
+          <t>Medición acústica (si aplica)</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Tecnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -1138,38 +1243,152 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="B15" s="8" t="inlineStr">
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Hojas de reclamaciones oficiales y su cartel anunciador</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>1 día</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>El modelo y el texto del cartel los aprueba tu Comunidad Autónoma</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>Contrato con gestor autorizado de residuos</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>2 semanas</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>Se comprueba en la inspección. Cartón, orgánico y el aceite usado de plancha y freidora, que no puede ir al desagüe</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Contrato de desinsectación, desratización y desinfección (DDD)</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>1 semana</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>Empresa inscrita en el ROESB; el certificado forma parte del plan APPCC</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="45" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Cartel y contrato de videovigilancia con la empresa de seguridad</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>Con la obra</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>Cartel homologado en zona visible, contrato de encargado de tratamiento y plazo máximo de conservación de 30 días</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C15">
-        <f>COUNTIF(A5:A13,"✓")</f>
+      <c r="C19" s="14">
+        <f>COUNTIF(A5:A17,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E15">
-        <f>COUNTIF(B5:B13,"?*")</f>
-        <v>9.0</v>
+      <c r="E19" s="14">
+        <f>COUNTIF(B5:B17,"?*")-COUNTIF(A5:A17,"N/A")</f>
+        <v>13.0</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:E13">
+  <conditionalFormatting sqref="A5:E17">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$A5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A5:A17">
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="1" stopIfTrue="1" text="✓">
+      <formula>NOT(ISERROR(SEARCH("✓",A5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
       <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1202,8 +1421,8 @@
     <col width="40" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="90" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>CHECKLIST APERTURA — TAPAS BAR / GASTROBAR</t>
         </is>
@@ -1225,7 +1444,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>TRAMITE / ACCION</t>
+          <t>TRÁMITE / ACCIÓN</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1245,14 +1464,14 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Proyecto tecnico actividad clasificada</t>
+          <t>Proyecto técnico actividad clasificada</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -1272,7 +1491,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1299,14 +1518,14 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Instalacion electrica (potencia 20-25 kW)</t>
+          <t>Instalación eléctrica (potencia 20-25 kW)</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -1321,12 +1540,12 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Cocina industrial + climatizacion = alta potencia</t>
+          <t>Cocina industrial + climatización = alta potencia</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1348,19 +1567,19 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Critico en tapas bar: plancha, freidora generan mucho humo</t>
+          <t>Crítico en tapas bar: plancha, freidora generan mucho humo</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Fontaneria, evacuacion y trampa grasas</t>
+          <t>Fontanería, evacuación y trampa grasas</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1380,14 +1599,14 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Climatizacion (AA + calefaccion)</t>
+          <t>Climatización (AA + calefacción)</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -1407,14 +1626,14 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Instalacion grifos cerveza (4-6 grifos)</t>
+          <t>Instalación grifos cerveza (4-6 grifos)</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -1434,7 +1653,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1456,19 +1675,19 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Plancha, freidora, horno, salamandra, bano maria</t>
+          <t>Plancha, freidora, horno, salamandra y baño maría</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Compra equipamiento frio</t>
+          <t>Compra equipamiento frío</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -1483,19 +1702,19 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Camara + neveras bajo barra + congelador</t>
+          <t>Cámara + neveras bajo barra + congelador</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Construccion barra + mostrador tapas</t>
+          <t>Construcción barra + mostrador tapas</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -1515,7 +1734,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1542,14 +1761,14 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Instalacion TPV + comandero</t>
+          <t>Instalación TPV + comandero</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -1569,14 +1788,14 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Decoracion, iluminacion, pizarras</t>
+          <t>Decoración, iluminación, pizarras</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -1591,7 +1810,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Azulejos, madera, pizarras tapas del dia</t>
+          <t>Azulejos, madera, pizarras tapas del día</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1821,7 @@
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C19">
+      <c r="C19" s="14">
         <f>COUNTIF(A5:A17,"✓")</f>
         <v>0.0</v>
       </c>
@@ -1611,12 +1830,13 @@
           <t>de</t>
         </is>
       </c>
-      <c r="E19">
-        <f>COUNTIF(B5:B17,"?*")</f>
+      <c r="E19" s="14">
+        <f>COUNTIF(B5:B17,"?*")-COUNTIF(A5:A17,"N/A")</f>
         <v>13.0</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
@@ -1625,8 +1845,13 @@
       <formula>$A5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A5:A17">
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="1" stopIfTrue="1" text="✓">
+      <formula>NOT(ISERROR(SEARCH("✓",A5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
       <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1649,7 +1874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1659,8 +1884,8 @@
     <col width="40" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="90" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>CHECKLIST APERTURA — TAPAS BAR / GASTROBAR</t>
         </is>
@@ -1669,7 +1894,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FASE 4: PERSONAL Y FORMACION</t>
+          <t>FASE 4: PERSONAL Y FORMACIÓN</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1907,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>TRAMITE / ACCION</t>
+          <t>TRÁMITE / ACCIÓN</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1702,7 +1927,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1729,7 +1954,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1756,14 +1981,14 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Seleccion y entrevistas</t>
+          <t>Selección y entrevistas</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -1778,12 +2003,12 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Prueba practica: elaborar 3 tapas en 20 min</t>
+          <t>Prueba práctica: elaborar 3 tapas en 20 min</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1800,17 +2025,17 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>1 día</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Convenio provincial hosteleria</t>
+          <t>Convenio provincial hostelería</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1832,51 +2057,51 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Minimo 1 dia antes de empezar</t>
+          <t>Mínimo 1 día antes de empezar</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Carnet manipulador alimentos</t>
+          <t>Formación en higiene alimentaria de todo el equipo</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>Titular</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>1 día</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Obligatorio todo personal, curso online valido</t>
+          <t>El «carnet de manipulador» está derogado (RD 109/2010): la formación la acredita la EMPRESA y se documenta en el plan APPCC</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Plan prevencion riesgos (PRL)</t>
+          <t>Plan prevención riesgos (PRL)</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>Titular o servicio ajeno</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -1886,19 +2111,19 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Servicio Prevencion Ajeno obligatorio</t>
+          <t>El plan de prevención es obligatorio; el proveedor externo, no: con menos de 25 trabajadores y un solo centro el titular puede asumir la actividad preventiva (art. 30.5 de la Ley 31/1995 y art. 11 del RD 39/1997)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Formacion cocina tapas</t>
+          <t>Formación cocina tapas</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -1918,14 +2143,14 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Formacion servicio y barra</t>
+          <t>Formación servicio y barra</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -1945,14 +2170,14 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Formacion alergenos + APPCC</t>
+          <t>Formación alérgenos + APPCC</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -1962,47 +2187,107 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>1 día</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>14 alergenos, registro temperaturas, trazabilidad</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="B16" s="8" t="inlineStr">
+          <t>14 alérgenos, registro temperaturas, trazabilidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Registro horario diario de la jornada de todo el equipo</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Gestor</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>Desde el primer contrato</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>Art. 34.9 del Estatuto de los Trabajadores; se conserva cuatro años</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="45" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>Informar al equipo del registro horario y del tratamiento de sus datos</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>Gestor</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>Desde el primer contrato</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>La cláusula informativa se entrega con el contrato; el fichaje es un tratamiento de datos, no sólo una obligación laboral</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C16">
-        <f>COUNTIF(A5:A14,"✓")</f>
+      <c r="C18" s="14">
+        <f>COUNTIF(A5:A16,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E16">
-        <f>COUNTIF(B5:B14,"?*")</f>
-        <v>10.0</v>
+      <c r="E18" s="14">
+        <f>COUNTIF(B5:B16,"?*")-COUNTIF(A5:A16,"N/A")</f>
+        <v>12.0</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:E14">
+  <conditionalFormatting sqref="A5:E16">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$A5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A5:A16">
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="1" stopIfTrue="1" text="✓">
+      <formula>NOT(ISERROR(SEARCH("✓",A5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
       <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2025,7 +2310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2035,8 +2320,8 @@
     <col width="40" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="90" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>CHECKLIST APERTURA — TAPAS BAR / GASTROBAR</t>
         </is>
@@ -2058,7 +2343,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>TRAMITE / ACCION</t>
+          <t>TRÁMITE / ACCIÓN</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -2078,19 +2363,19 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Disenar identidad visual</t>
+          <t>Diseñar identidad visual</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Disenador</t>
+          <t>Diseñador</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -2100,19 +2385,19 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Logo, colores, tipografia, estilo visual</t>
+          <t>Logo, colores, tipografía y estilo visual</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Ficha Google My Business (CRITICO)</t>
+          <t>Ficha Google My Business (CRÍTICO)</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -2122,17 +2407,17 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>1 día</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Categoria: Bar de tapas. Fotos, horario, carta</t>
+          <t>Categoría: Bar de tapas. Fotos, horario, carta</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -2149,29 +2434,29 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>1 día</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Instagram para fotos tapas, TikTok para videos cocina</t>
+          <t>Instagram para fotos de tapas, TikTok para vídeos de cocina</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Pagina web basica</t>
+          <t>Página web básica</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Dev/Disenador</t>
+          <t>Dev/Diseñador</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -2181,29 +2466,29 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Con carta, ubicacion, reservas, horario</t>
+          <t>Con carta, ubicación, reservas, horario</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Sesion fotos profesional</t>
+          <t>Sesión fotos profesional</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Fotografo</t>
+          <t>Fotógrafo</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>1 día</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -2213,19 +2498,19 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Disenar carta / pizarras tapas</t>
+          <t>Diseñar carta / pizarras tapas</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Disenador</t>
+          <t>Diseñador</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -2235,19 +2520,19 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Carta fisica + pizarra tapas del dia + QR digital</t>
+          <t>Carta física + pizarra de tapas del día + QR digital</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Rotulacion exterior</t>
+          <t>Rotulación exterior</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -2262,19 +2547,19 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Rotulo + pizarra exterior + vinilo</t>
+          <t>Rótulo + pizarra exterior + vinilo</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Campana pre-apertura RRSS</t>
+          <t>Campaña pre-apertura RRSS</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -2289,12 +2574,12 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Behind the scenes, cuenta atras, sorteo inaugural</t>
+          <t>Cocina a la vista, cuenta atrás y sorteo inaugural</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -2321,7 +2606,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -2338,7 +2623,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>1 día</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -2348,14 +2633,14 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Evento inauguracion</t>
+          <t>Evento inauguración</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -2365,7 +2650,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>1 día</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -2375,14 +2660,14 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Programa fidelizacion</t>
+          <t>Programa fidelización</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -2401,38 +2686,98 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="B18" s="8" t="inlineStr">
+    <row r="17" ht="75" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Licencia de derechos de autor por la música ambiental (SGAE/AGEDI-AIE)</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>2 semanas</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>Distinta de la licencia municipal de música que ya tiene este checklist: ésta es de propiedad intelectual y se paga aunque el ayuntamiento ya haya autorizado el hilo musical o el DJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="45" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>Cláusula informativa y consentimiento en TheFork y en la lista de correo</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>Antes de abrir</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>TheFork, WhatsApp y newsletter tratan datos: cada canal necesita su información previa</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C18">
-        <f>COUNTIF(A5:A16,"✓")</f>
+      <c r="C20" s="14">
+        <f>COUNTIF(A5:A18,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E18">
-        <f>COUNTIF(B5:B16,"?*")</f>
-        <v>12.0</v>
+      <c r="E20" s="14">
+        <f>COUNTIF(B5:B18,"?*")-COUNTIF(A5:A18,"N/A")</f>
+        <v>14.0</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:E16">
+  <conditionalFormatting sqref="A5:E18">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$A5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A5:A18">
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="1" stopIfTrue="1" text="✓">
+      <formula>NOT(ISERROR(SEARCH("✓",A5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
       <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2465,8 +2810,8 @@
     <col width="40" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="90" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>CHECKLIST APERTURA — TAPAS BAR / GASTROBAR</t>
         </is>
@@ -2475,7 +2820,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FASE 6: PRIMEROS 90 DIAS</t>
+          <t>FASE 6: PRIMEROS 90 DÍAS</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2833,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>TRAMITE / ACCION</t>
+          <t>TRÁMITE / ACCIÓN</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -2508,14 +2853,14 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Revision diaria caja y ventas</t>
+          <t>Revisión diaria caja y ventas</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -2535,7 +2880,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -2557,19 +2902,19 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Pesar genero: carnes, pescado, embutidos</t>
+          <t>Pesar el género: carnes, pescado y embutidos</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Analisis tapas mas vendidas vs menos vendidas</t>
+          <t>Análisis de las tapas más vendidas frente a las menos vendidas</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -2584,19 +2929,19 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Aplicar ingenieria de menu: Stars, Puzzles, Dogs</t>
+          <t>Aplicar ingeniería de menú: Stars, Puzzles, Dogs</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Ajustar carta tapas del dia</t>
+          <t>Ajustar carta tapas del día</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -2611,19 +2956,19 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Rotar tapas segun temporada y producto disponible</t>
+          <t>Rotar tapas según temporada y producto disponible</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Encuestas clientes + resenas Google</t>
+          <t>Encuestas clientes + reseñas Google</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2638,12 +2983,12 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Pedir resenas, responder TODAS</t>
+          <t>Pedir reseñas, responder TODAS</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -2665,12 +3010,12 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Reforzar viernes-sabado, reducir lunes-martes</t>
+          <t>Reforzar viernes-sábado, reducir lunes-martes</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -2697,7 +3042,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -2724,7 +3069,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -2751,7 +3096,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -2784,7 +3129,7 @@
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C16">
+      <c r="C16" s="14">
         <f>COUNTIF(A5:A14,"✓")</f>
         <v>0.0</v>
       </c>
@@ -2793,12 +3138,13 @@
           <t>de</t>
         </is>
       </c>
-      <c r="E16">
-        <f>COUNTIF(B5:B14,"?*")</f>
+      <c r="E16" s="14">
+        <f>COUNTIF(B5:B14,"?*")-COUNTIF(A5:A14,"N/A")</f>
         <v>10.0</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
@@ -2807,8 +3153,13 @@
       <formula>$A5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A5:A14">
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="1" stopIfTrue="1" text="✓">
+      <formula>NOT(ISERROR(SEARCH("✓",A5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
       <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2823,4 +3174,96 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="110" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>INSTRUCCIONES DE USO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Este fichero forma parte del producto «plan-negocio-tapas-bar» de AI Chef Pro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Las celdas VERDES son las editables: cambia esas y el resto del libro se recalcula solo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Columna OK: elige ✓ (hecho), ☐ (pendiente) o N/A (no aplica). Las N/A no cuentan en el total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>El contador de cada pestaña cuenta sólo las ✓; las N/A salen del total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Para editar una celda que no esté en verde: Revisar → Desproteger hoja (no tiene contraseña).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>Más plantillas y kits del catálogo en aichef.pro/productos-digitales</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>Versión 2.2 · septiembre 2026 · aichef.pro/plan-negocio-tapas-bar · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
 </file>